--- a/tests/workbooktests/workbooks/test_convertiblebonds.xlsx
+++ b/tests/workbooktests/workbooks/test_convertiblebonds.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEC8467-6A43-4737-94D4-BA5F377971F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F7B273-20F1-49A9-A79B-A8303E76B211}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7290" yWindow="-21285" windowWidth="30255" windowHeight="16650" xr2:uid="{B3EEA080-4589-4824-92D0-D334717E2C8E}"/>
   </bookViews>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -38,30 +27,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Today</t>
   </si>
@@ -208,13 +175,16 @@
   </si>
   <si>
     <t>Float w/ callability</t>
+  </si>
+  <si>
+    <t>{=qlScheduleDates(B18)}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -269,9 +239,12 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -604,13 +577,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0A4FE2-3664-4C38-8DF2-99DF28E9CC8F}">
   <dimension ref="A1:G60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -618,43 +591,43 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" cm="1">
+      <c r="B2" s="1">
         <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
+      <c r="B4" s="2" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlFlatForward(B2,0.01)</f>
+      <c r="B5" s="2" t="str">
+        <f>_xll.qlFlatForward(B2,0.01,"actual365fixed")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="str" cm="1">
+      <c r="B6" s="2" t="str">
         <f t="array" ref="B6">_xll.qlBlackConstantVol(B2,"NullCalendar",0.25,"Act/365")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R6C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -662,105 +635,99 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="str" cm="1">
+      <c r="B9" s="2" t="str">
         <f t="array" ref="B9">_xll.qlGeneralizedBlackScholesProcess(B7,B5,B4,B6)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R9C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="2" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlFlatForward(B10,0.03)</f>
+      <c r="B12" s="2" t="str">
+        <f>_xll.qlFlatForward(B10,0.03,"actual365fixed")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R12C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="2" t="str" cm="1">
+      <c r="B13" s="2" t="str">
         <f t="array" ref="B13">_xll.qlEuribor("3m",B12)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R13C2Euribor,A</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="1" cm="1">
+      <c r="B16" s="1">
         <f t="array" ref="B16">_xll.qlCalendarAdvance("NullCalendar",B2,"5y")</f>
         <v>48000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="1" cm="1">
+      <c r="B17" s="1">
         <f t="array" ref="B17">_xll.qlCalendarAdvance("NullCalendar",B2,"9y")</f>
         <v>49461</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1" t="str" cm="1">
+      <c r="B18" s="1" t="str">
         <f t="array" ref="B18">_xll.qlMakeSchedule(B16,B17,"1y",,"Target")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R18C2Schedule,A</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" cm="1">
-        <f t="array" ref="B19:B23">_xll.qlScheduleDates(B18)</f>
+    <row r="19" spans="1:2">
+      <c r="B19" s="1">
+        <f>_xll.qlScheduleDates(B18)</f>
         <v>48001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="1">
-        <v>48366</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B21" s="1">
-        <v>48731</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B22" s="1">
-        <v>49096</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B23" s="1">
-        <v>49461</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
+      <c r="B20" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="2" t="str" cm="1">
+      <c r="B24" s="2" t="str">
         <f t="array" ref="B24">_xll.qlBermudanExercise(B19:B23)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R24C2BermudanExercise,A</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="2" t="str" cm="1">
+      <c r="B25" s="2" t="str">
         <f t="array" ref="B25">_xll.qlEuropeanExercise(B16)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R25C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -768,22 +735,22 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="2" t="str" cm="1">
+      <c r="B27" s="2" t="str">
         <f t="array" ref="B27">_xll.qlCallability(_xll.qlBondPrice(100,"Clean"),"call",B19)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R27C2Callability,A</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="str" cm="1">
+    <row r="28" spans="1:2">
+      <c r="B28" s="2" t="str">
         <f t="array" ref="B28">_xll.qlCallability(_xll.qlBondPrice(100,"Clean"),"call",B21)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R28C2Callability,A</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -792,7 +759,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -800,7 +767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -808,34 +775,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="1" cm="1">
+      <c r="B32" s="1">
         <f t="array" ref="B32">_xll.qlCalendarAdvance("Target",B29,"10y")</f>
         <v>49837</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="2" t="str" cm="1">
+      <c r="B33" s="2" t="str">
         <f t="array" ref="B33">_xll.qlMakeSchedule(B29,B32,"1y",,"Target")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R33C2Schedule,A</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="2" t="str" cm="1">
+      <c r="B34" s="2" t="str">
         <f t="array" ref="B34">_xll.qlMakeSchedule(B29,B32,"3m",,"Target")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R34C2Schedule,A</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -843,66 +810,66 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="2" t="str" cm="1">
+      <c r="B37" s="2" t="str">
         <f t="array" ref="B37">_xll.qlConvertibleZeroCouponBond(B24,B26,B29,B30,"30/360",B33,B35)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R37C2ConvertibleZeroCouponBond,A</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="2" t="str" cm="1">
+      <c r="B38" s="2" t="str">
         <f t="array" ref="B38">_xll.qlConvertibleZeroCouponBond(B24,B26,B29,B30,"30/360",B33,B35,B27:B28)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R38C2ConvertibleZeroCouponBond,A</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="str" cm="1">
-        <f t="array" ref="B40">_xll.qlConvertibleFixedCouponBond(B24,B26,B29,B30,0.03,"30/360",B33,B35)</f>
+      <c r="B40" s="2" t="str">
+        <f t="array" ref="B40">_xll.qlConvertibleFixedCouponBond(B24,B26,B29,B30,0.03,"30/360",B33,B35,"0D","Target")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R40C2ConvertibleFixedCouponBond,A</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="str" cm="1">
-        <f t="array" ref="B41">_xll.qlConvertibleFixedCouponBond(B24,B26,B29,B30,0.03,"30/360",B33,B35,,,,,B27:B28)</f>
+      <c r="B41" s="2" t="str">
+        <f t="array" ref="B41">_xll.qlConvertibleFixedCouponBond(B24,B26,B29,B30,0.03,"30/360",B33,B35,"0D","Target",,,B27:B28)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R41C2ConvertibleFixedCouponBond,A</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="2" t="str" cm="1">
-        <f t="array" ref="B43">_xll.qlConvertibleFloatingRateBond(B24,B26,B29,B30,B13,B31,0,"Act/360",B34,B35)</f>
+      <c r="B43" s="2" t="str">
+        <f t="array" ref="B43">_xll.qlConvertibleFloatingRateBond(B24,B26,B29,B30,B13,B31,0,"Act/360",B34,B35,"0D","Target")</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R43C2ConvertibleFloatingRateBond,A</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="2" t="str" cm="1">
-        <f t="array" ref="B44">_xll.qlConvertibleFloatingRateBond(B24,B26,B29,B30,B13,B31,0,"Act/360",B34,B35,,,,,B27:B28)</f>
-        <v>欣[test_convertiblebonds.xlsx]Sheet1!R44C2ConvertibleFloatingRateBond,S</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="str">
+        <f t="array" ref="B44">_xll.qlConvertibleFloatingRateBond(B24,B26,B29,B30,B13,B31,0,"Act/360",B34,B35,"0D","Target",,,B27:B28)</f>
+        <v>欣[test_convertiblebonds.xlsx]Sheet1!R44C2ConvertibleFloatingRateBond,A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15">
       <c r="A46" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -914,7 +881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -925,7 +892,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -936,7 +903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -947,7 +914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -955,72 +922,72 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="15">
       <c r="A52" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B52" s="2" t="str" cm="1">
+      <c r="B52" s="2" t="str">
         <f t="array" ref="B52">_xll.qlBinomialConvertibleEngine(B47,B48,B49,B50)</f>
         <v>欣[test_convertiblebonds.xlsx]Sheet1!R52C2BinomialCRRConvertibleEngine,A</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="15">
       <c r="A54" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="6" cm="1">
+      <c r="B55" s="6">
         <f t="array" ref="B55">_xll.qlInstrumentNPV(B37,_xll.qlInstrumentSetPricingEngine(B37,$B$52))</f>
-        <v>11046.869977387039</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11081.337113450401</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="B56" s="6" cm="1">
+      <c r="B56" s="6">
         <f t="array" ref="B56">_xll.qlInstrumentNPV(B38,_xll.qlInstrumentSetPricingEngine(B38,$B$52))</f>
-        <v>9519.443481791357</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>43</v>
       </c>
-      <c r="B57" s="6" cm="1">
+      <c r="B57" s="6">
         <f t="array" ref="B57">_xll.qlInstrumentNPV(B40,_xll.qlInstrumentSetPricingEngine(B40,$B$52))</f>
-        <v>11067.80952084887</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11101.465444821617</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>44</v>
       </c>
-      <c r="B58" s="6" cm="1">
+      <c r="B58" s="6">
         <f t="array" ref="B58">_xll.qlInstrumentNPV(B41,_xll.qlInstrumentSetPricingEngine(B41,$B$52))</f>
-        <v>9530.587049288697</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>47</v>
       </c>
-      <c r="B59" s="6" cm="1">
+      <c r="B59" s="6">
         <f t="array" ref="B59">_xll.qlInstrumentNPV(B43,_xll.qlInstrumentSetPricingEngine(B43,$B$52))</f>
-        <v>11068.96500408951</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11102.529015531909</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>48</v>
       </c>
-      <c r="B60" s="6" cm="1">
+      <c r="B60" s="6">
         <f t="array" ref="B60">_xll.qlInstrumentNPV(B44,_xll.qlInstrumentSetPricingEngine(B44,$B$52))</f>
-        <v>9532.7273553674495</v>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
